--- a/data-manipulation-scripts/sheets-cleanup/sheets/CARENAGEM - 18_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/CARENAGEM - 18_01.xlsx
@@ -477,7 +477,9 @@
       <c r="C2" s="4">
         <v>1.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="4">
+        <v>188.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
